--- a/Support Files/Accounts/Account Templates/SAT_2025.xlsx
+++ b/Support Files/Accounts/Account Templates/SAT_2025.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/l00792192/Library/Mobile Documents/com~apple~CloudDocs/Documents/Desarrollos/MyAccountingBooks/Documentos de apoyo/Templates de Cuentas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lguevara/Documents/Desarrollos/MyAccountingBooks/Support Files/Accounts/Account Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4076D79-D6A2-6C4B-B4FD-9A7F3A1B6E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D5F884-CED5-D440-98FF-2987C75FC47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3380" yWindow="3080" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="SAT Agrupador 2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Nodes" sheetId="1" r:id="rId1"/>
+    <sheet name="Meta" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4288" uniqueCount="1817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4303" uniqueCount="1832">
   <si>
     <t>Kind</t>
   </si>
@@ -5471,6 +5472,51 @@
   </si>
   <si>
     <t>800.00.817.02</t>
+  </si>
+  <si>
+    <t>MX</t>
+  </si>
+  <si>
+    <t>es-MX</t>
+  </si>
+  <si>
+    <t>SAT_2025</t>
+  </si>
+  <si>
+    <t>SAT 2025 Business Chart of Accounts (Agrupador-based)</t>
+  </si>
+  <si>
+    <t>SAT (Mexico) agrupador-based business chart of accounts, 2025 edition</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>locale</t>
+  </si>
+  <si>
+    <t>industry</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>SYSTEM</t>
   </si>
 </sst>
 </file>
@@ -5576,6 +5622,17 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Role"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Type"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Placeholder"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{046BF3D3-B52F-BC41-A6ED-693C9C0D3883}" name="Table3" displayName="Table3" ref="A1:B8" totalsRowShown="0">
+  <autoFilter ref="A1:B8" xr:uid="{046BF3D3-B52F-BC41-A6ED-693C9C0D3883}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{C9E4B0B5-8702-3F4B-B081-8206B43AE04F}" name="Key"/>
+    <tableColumn id="2" xr3:uid="{56A29130-F728-D240-A578-02E31FC7F071}" name="Value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5812,6 +5869,9 @@
       <c r="F2">
         <v>0</v>
       </c>
+      <c r="G2" t="s">
+        <v>1831</v>
+      </c>
       <c r="H2">
         <v>1</v>
       </c>
@@ -33709,4 +33769,87 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2785D08-85ED-4B41-BA40-ECC49926FF2F}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="55.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" customWidth="1"/>
+    <col min="4" max="4" width="17.1640625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>